--- a/Result/profitability/1220.xlsx
+++ b/Result/profitability/1220.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.12</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06125</v>
+        <v>0.02499999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>10.5475</v>
+        <v>9.516249999999999</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006249999999999995</v>
+        <v>-0.002500000000000004</v>
       </c>
       <c r="N3" t="n">
-        <v>8.380000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.28</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.04375000000000001</v>
+        <v>-0.02500000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>8.465</v>
+        <v>8.866249999999999</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.58</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.10375</v>
+        <v>-0.09625</v>
       </c>
       <c r="N5" t="n">
-        <v>3.91125</v>
+        <v>3.691249999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.12375</v>
+        <v>-0.1475</v>
       </c>
       <c r="N6" t="n">
-        <v>2.345</v>
+        <v>1.525</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1575</v>
+        <v>-0.145</v>
       </c>
       <c r="N7" t="n">
-        <v>1.29875</v>
+        <v>1.4725</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.02</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.15375</v>
+        <v>-0.12625</v>
       </c>
       <c r="N8" t="n">
-        <v>1.2425</v>
+        <v>1.4625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>-0.13625</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3812500000000001</v>
+        <v>0.3812499999999997</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>-0.14875</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1025000000000003</v>
+        <v>0.1024999999999998</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>811</v>
+      </c>
+      <c r="D75" t="n">
+        <v>734</v>
+      </c>
+      <c r="E75" t="n">
+        <v>77</v>
+      </c>
+      <c r="F75" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>10</v>
+      </c>
+      <c r="J75" t="n">
+        <v>11</v>
+      </c>
+      <c r="K75" t="n">
+        <v>8</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="N75" t="n">
+        <v>10.77625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.294117647058824</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.760000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2259306803594352</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1556145004420866</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
